--- a/business_card_result.xlsx
+++ b/business_card_result.xlsx
@@ -425,78 +425,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>会社名</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>郵便番号</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>住所</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>電話番号</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>E-mail</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
+          <t>値</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>会社名</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>株式会社モダントラベル</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>桜井紀子</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>郵便番号</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>〒123-4567</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>住所</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>千葉県大原市東海岸通り1丁目2-3</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>01-2345-6789</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>hello@subarashiisaito.co.jp</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>www.subarashiisaito.co.jp</t>
         </is>
